--- a/data/trans_orig/P36B10-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B10-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2007</t>
+          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2007 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53633</t>
+          <t>53891</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87216</t>
+          <t>86354</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105060</t>
+          <t>103435</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>148900</t>
+          <t>146717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>168283</t>
+          <t>168065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>224525</t>
+          <t>222371</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132044</t>
+          <t>130767</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>177464</t>
+          <t>176232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>213645</t>
+          <t>213194</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271370</t>
+          <t>268474</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>361271</t>
+          <t>356673</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>433068</t>
+          <t>430543</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>330005</t>
+          <t>328775</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>390828</t>
+          <t>391373</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>463542</t>
+          <t>465677</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>535161</t>
+          <t>535545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>818639</t>
+          <t>819753</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>910716</t>
+          <t>913189</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,01%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>267900</t>
+          <t>271640</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>328896</t>
+          <t>330369</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>280598</t>
+          <t>285586</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>342092</t>
+          <t>347446</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>567565</t>
+          <t>568082</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>648656</t>
+          <t>652992</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>126771</t>
+          <t>127088</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>169747</t>
+          <t>170224</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113646</t>
+          <t>112432</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>157177</t>
+          <t>156339</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>250011</t>
+          <t>251660</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>309460</t>
+          <t>312113</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49403</t>
+          <t>49729</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81289</t>
+          <t>83084</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95377</t>
+          <t>92803</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135596</t>
+          <t>136944</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>153240</t>
+          <t>153458</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>207132</t>
+          <t>204208</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>129657</t>
+          <t>130653</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>176662</t>
+          <t>177343</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226570</t>
+          <t>228747</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>286925</t>
+          <t>286790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>373568</t>
+          <t>373291</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>449287</t>
+          <t>449039</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>431681</t>
+          <t>434442</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>508702</t>
+          <t>507971</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>635265</t>
+          <t>631745</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>709743</t>
+          <t>710452</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1085121</t>
+          <t>1083684</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1197767</t>
+          <t>1195300</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>488678</t>
+          <t>490581</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>566542</t>
+          <t>568201</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>349279</t>
+          <t>352527</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>416394</t>
+          <t>422191</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>860980</t>
+          <t>867347</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>969132</t>
+          <t>966718</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>436323</t>
+          <t>436579</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>512885</t>
+          <t>507597</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>128511</t>
+          <t>129015</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174331</t>
+          <t>176686</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>578138</t>
+          <t>581577</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>668075</t>
+          <t>666567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27082</t>
+          <t>26015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53887</t>
+          <t>51987</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26954</t>
+          <t>26736</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51069</t>
+          <t>51599</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>59305</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94909</t>
+          <t>94082</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61225</t>
+          <t>60850</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94773</t>
+          <t>95663</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61642</t>
+          <t>61119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>94755</t>
+          <t>95170</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>129453</t>
+          <t>127826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>175129</t>
+          <t>177403</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>168014</t>
+          <t>170341</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>214822</t>
+          <t>217250</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>191162</t>
+          <t>193442</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>235758</t>
+          <t>236644</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>376300</t>
+          <t>375076</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>438273</t>
+          <t>437446</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>149321</t>
+          <t>150588</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>196287</t>
+          <t>193271</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>93470</t>
+          <t>93887</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>133172</t>
+          <t>131338</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>255238</t>
+          <t>256167</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>313784</t>
+          <t>316666</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57385</t>
+          <t>56492</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>89909</t>
+          <t>89412</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26903</t>
+          <t>27650</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50672</t>
+          <t>51207</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,47 +2598,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>10,75%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>109314</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>89714</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>129495</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>10,64%</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>109314</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>91077</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>127992</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>10,64%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>147149</t>
+          <t>146854</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>200076</t>
+          <t>201403</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>244383</t>
+          <t>244787</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>312451</t>
+          <t>311349</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>405475</t>
+          <t>411102</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>489687</t>
+          <t>490867</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>348060</t>
+          <t>348305</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>420463</t>
+          <t>421152</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>531170</t>
+          <t>534591</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>616837</t>
+          <t>618567</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>902598</t>
+          <t>898898</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1020596</t>
+          <t>1015347</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>970170</t>
+          <t>974825</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1076535</t>
+          <t>1079092</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1328606</t>
+          <t>1329416</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1442506</t>
+          <t>1445801</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2335280</t>
+          <t>2338408</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2486404</t>
+          <t>2493953</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>955487</t>
+          <t>946254</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1055005</t>
+          <t>1051415</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>759735</t>
+          <t>760839</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>857937</t>
+          <t>857056</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1731404</t>
+          <t>1731085</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1877420</t>
+          <t>1879996</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>644436</t>
+          <t>644680</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>736558</t>
+          <t>735910</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>289430</t>
+          <t>290864</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>353938</t>
+          <t>358949</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>962791</t>
+          <t>959103</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1074178</t>
+          <t>1067055</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2012</t>
+          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2012 (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77288</t>
+          <t>78235</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>116548</t>
+          <t>115786</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>178120</t>
+          <t>176990</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>236244</t>
+          <t>232538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>267838</t>
+          <t>268164</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>336927</t>
+          <t>335866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>243063</t>
+          <t>239115</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>301060</t>
+          <t>300017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>387074</t>
+          <t>386480</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>453487</t>
+          <t>454981</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>647016</t>
+          <t>643894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>739373</t>
+          <t>733183</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>257773</t>
+          <t>259415</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>315959</t>
+          <t>317164</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>365347</t>
+          <t>364305</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>430778</t>
+          <t>432205</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>635229</t>
+          <t>636528</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>719976</t>
+          <t>726603</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>189197</t>
+          <t>189842</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>243430</t>
+          <t>242002</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>175115</t>
+          <t>178851</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229972</t>
+          <t>231398</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>382678</t>
+          <t>384612</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>461682</t>
+          <t>458957</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79929</t>
+          <t>78576</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116874</t>
+          <t>115589</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82186</t>
+          <t>81252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>122439</t>
+          <t>120900</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170440</t>
+          <t>171462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>228807</t>
+          <t>225035</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94446</t>
+          <t>96131</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>137368</t>
+          <t>140077</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127665</t>
+          <t>128550</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>178086</t>
+          <t>178193</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>233287</t>
+          <t>237752</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>301716</t>
+          <t>306208</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>291895</t>
+          <t>287915</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>359178</t>
+          <t>356123</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>386654</t>
+          <t>385304</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>463176</t>
+          <t>458440</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>694631</t>
+          <t>694571</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>791831</t>
+          <t>796543</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>554919</t>
+          <t>551914</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>637649</t>
+          <t>638772</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>531789</t>
+          <t>533495</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>612570</t>
+          <t>611815</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1106973</t>
+          <t>1109363</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1222630</t>
+          <t>1224501</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>535553</t>
+          <t>535255</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>615603</t>
+          <t>619090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>368733</t>
+          <t>371521</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>444053</t>
+          <t>444094</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>926158</t>
+          <t>927681</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1038438</t>
+          <t>1035466</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315120</t>
+          <t>313311</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>384236</t>
+          <t>388018</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170451</t>
+          <t>171613</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>225850</t>
+          <t>226000</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>504757</t>
+          <t>505365</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>594385</t>
+          <t>594739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19294</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41081</t>
+          <t>39906</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29264</t>
+          <t>29363</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56904</t>
+          <t>56583</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54134</t>
+          <t>53844</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88930</t>
+          <t>90096</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84967</t>
+          <t>85485</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126505</t>
+          <t>126184</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98271</t>
+          <t>98122</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>140329</t>
+          <t>139660</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>196983</t>
+          <t>196248</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>251736</t>
+          <t>251883</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,95%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>129823</t>
+          <t>129029</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>173013</t>
+          <t>175384</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>145084</t>
+          <t>145049</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>190892</t>
+          <t>187215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>286768</t>
+          <t>286390</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>346086</t>
+          <t>347551</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120534</t>
+          <t>120392</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>164114</t>
+          <t>163455</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>70893</t>
+          <t>71262</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>105405</t>
+          <t>107064</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>202475</t>
+          <t>203769</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>257573</t>
+          <t>259263</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38942</t>
+          <t>39061</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67144</t>
+          <t>68524</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>30586</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57585</t>
+          <t>57061</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77091</t>
+          <t>77870</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>114688</t>
+          <t>116735</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>208082</t>
+          <t>211473</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>268929</t>
+          <t>275906</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>358581</t>
+          <t>360218</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>439950</t>
+          <t>442438</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>589472</t>
+          <t>580533</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>690403</t>
+          <t>684315</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>639447</t>
+          <t>646609</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>743688</t>
+          <t>746761</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>905875</t>
+          <t>905871</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1015259</t>
+          <t>1015846</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1585198</t>
+          <t>1584517</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1736536</t>
+          <t>1727181</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>974757</t>
+          <t>975194</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1091711</t>
+          <t>1093237</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,47 +5978,47 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>32,14%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1042</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1133269</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>1075447</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>1191793</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>32,1%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1042</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>1133269</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>1079751</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1196252</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>32,1%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2079263</t>
+          <t>2087497</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2246754</t>
+          <t>2242476</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>875722</t>
+          <t>876996</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>985404</t>
+          <t>985685</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>653444</t>
+          <t>652446</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>754175</t>
+          <t>754642</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1555031</t>
+          <t>1562117</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1703691</t>
+          <t>1705565</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>458256</t>
+          <t>457129</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>538771</t>
+          <t>540796</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>306100</t>
+          <t>303402</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>378490</t>
+          <t>377299</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>780216</t>
+          <t>780195</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>892528</t>
+          <t>889479</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2016</t>
+          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2016 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58717</t>
+          <t>60797</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91028</t>
+          <t>91366</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110241</t>
+          <t>110107</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>154459</t>
+          <t>152725</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>178531</t>
+          <t>180033</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>233459</t>
+          <t>232198</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>127369</t>
+          <t>127274</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169541</t>
+          <t>171055</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234099</t>
+          <t>234432</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>292632</t>
+          <t>292124</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>376087</t>
+          <t>376332</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>449840</t>
+          <t>446353</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>250210</t>
+          <t>248223</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>302401</t>
+          <t>300566</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>323900</t>
+          <t>325867</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>387986</t>
+          <t>387071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>589421</t>
+          <t>589181</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>671189</t>
+          <t>674171</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>151751</t>
+          <t>153725</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>198587</t>
+          <t>200575</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>169313</t>
+          <t>166798</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>220438</t>
+          <t>221007</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>334319</t>
+          <t>337997</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>402438</t>
+          <t>405020</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,22%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64560</t>
+          <t>61951</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97727</t>
+          <t>96454</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36421</t>
+          <t>37034</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64441</t>
+          <t>65086</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>106671</t>
+          <t>106879</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>152263</t>
+          <t>153300</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80712</t>
+          <t>80053</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124446</t>
+          <t>119161</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124566</t>
+          <t>127747</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>175387</t>
+          <t>172702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>217548</t>
+          <t>216838</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>283944</t>
+          <t>282441</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>276975</t>
+          <t>274777</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>341993</t>
+          <t>343317</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>367652</t>
+          <t>370393</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>441881</t>
+          <t>444692</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>669601</t>
+          <t>670469</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>762705</t>
+          <t>765528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>748833</t>
+          <t>748205</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>839846</t>
+          <t>836197</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>721631</t>
+          <t>722452</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>813182</t>
+          <t>806369</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1500113</t>
+          <t>1495298</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1620063</t>
+          <t>1624565</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>567371</t>
+          <t>565592</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>650959</t>
+          <t>648939</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>459484</t>
+          <t>455730</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>539190</t>
+          <t>533184</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1047241</t>
+          <t>1051676</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1163626</t>
+          <t>1168211</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>228721</t>
+          <t>229740</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>294693</t>
+          <t>292811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141106</t>
+          <t>140208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>189751</t>
+          <t>190494</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>384598</t>
+          <t>383893</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>463690</t>
+          <t>465044</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31425</t>
+          <t>30988</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57408</t>
+          <t>57991</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31174</t>
+          <t>32035</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59192</t>
+          <t>60106</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68295</t>
+          <t>69272</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107525</t>
+          <t>106814</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74669</t>
+          <t>74854</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111318</t>
+          <t>111750</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>99030</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139632</t>
+          <t>136776</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186446</t>
+          <t>188286</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>240472</t>
+          <t>242694</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>206468</t>
+          <t>204723</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>255964</t>
+          <t>253114</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>189173</t>
+          <t>188155</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>233832</t>
+          <t>234619</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>406706</t>
+          <t>406296</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>476646</t>
+          <t>472351</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,26%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>118151</t>
+          <t>116157</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>158200</t>
+          <t>159286</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>105948</t>
+          <t>107183</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>146056</t>
+          <t>147531</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>230999</t>
+          <t>237178</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>293300</t>
+          <t>292209</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28972</t>
+          <t>29366</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55342</t>
+          <t>57354</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37155</t>
+          <t>36725</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63594</t>
+          <t>62360</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71975</t>
+          <t>71615</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110102</t>
+          <t>110196</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>189301</t>
+          <t>188947</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>249626</t>
+          <t>249112</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>284519</t>
+          <t>288054</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>356630</t>
+          <t>359031</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>493187</t>
+          <t>493857</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>588347</t>
+          <t>587582</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>507713</t>
+          <t>510405</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>594348</t>
+          <t>594248</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>736841</t>
+          <t>734063</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>836033</t>
+          <t>843506</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1267860</t>
+          <t>1272733</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1404561</t>
+          <t>1408607</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1244230</t>
+          <t>1242251</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1359225</t>
+          <t>1358477</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,77 +8937,77 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>36,9%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>40,36%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1332734</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>1271560</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>1387809</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>37,85%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>36,11%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>39,41%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>2498</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2632434</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2545760</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>2713081</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>38,22%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>36,96%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>40,38%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1263</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>1332734</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>1269423</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1389779</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>37,85%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>36,05%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>39,46%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2498</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>2632434</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>2561062</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>2712865</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>38,22%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>37,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>868222</t>
+          <t>869509</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>973248</t>
+          <t>973870</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>767117</t>
+          <t>767730</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>867702</t>
+          <t>869862</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1662045</t>
+          <t>1657310</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1813222</t>
+          <t>1810773</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>341666</t>
+          <t>343343</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>419936</t>
+          <t>415281</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>232639</t>
+          <t>232673</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>291125</t>
+          <t>290679</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>593553</t>
+          <t>594060</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>693496</t>
+          <t>690296</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B10-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B10-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53891</t>
+          <t>54253</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86354</t>
+          <t>85279</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103435</t>
+          <t>106566</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146717</t>
+          <t>148040</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>168065</t>
+          <t>165639</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>222371</t>
+          <t>220814</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>130767</t>
+          <t>132608</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>176232</t>
+          <t>177447</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>213194</t>
+          <t>215665</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268474</t>
+          <t>271636</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>356673</t>
+          <t>361690</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>430543</t>
+          <t>433312</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>328775</t>
+          <t>329655</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>391373</t>
+          <t>389224</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>465677</t>
+          <t>465995</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>535545</t>
+          <t>537175</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>819753</t>
+          <t>812981</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>913189</t>
+          <t>906562</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>271640</t>
+          <t>269379</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>330369</t>
+          <t>329775</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>285586</t>
+          <t>282740</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>347446</t>
+          <t>345693</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>568082</t>
+          <t>571043</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>652992</t>
+          <t>652837</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>127088</t>
+          <t>127068</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>170224</t>
+          <t>171874</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>112432</t>
+          <t>112575</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>156339</t>
+          <t>156788</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>251660</t>
+          <t>251845</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>312113</t>
+          <t>312252</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49729</t>
+          <t>50381</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83084</t>
+          <t>83232</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92803</t>
+          <t>95331</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136944</t>
+          <t>135226</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>153458</t>
+          <t>153474</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204208</t>
+          <t>206389</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130653</t>
+          <t>129676</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>177343</t>
+          <t>178228</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>228747</t>
+          <t>228441</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>286790</t>
+          <t>286107</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>373291</t>
+          <t>371979</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>449039</t>
+          <t>446165</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>434442</t>
+          <t>434796</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>507971</t>
+          <t>509893</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>631745</t>
+          <t>632441</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>710452</t>
+          <t>710151</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1083684</t>
+          <t>1092376</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1195300</t>
+          <t>1198676</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,66%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>490581</t>
+          <t>491384</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>568201</t>
+          <t>571633</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>352527</t>
+          <t>353954</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>422191</t>
+          <t>421688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>867347</t>
+          <t>863670</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>966718</t>
+          <t>967882</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>436579</t>
+          <t>435611</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>507597</t>
+          <t>504608</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>129015</t>
+          <t>132095</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176686</t>
+          <t>174558</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>581577</t>
+          <t>581317</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>666567</t>
+          <t>669223</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26015</t>
+          <t>25147</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51987</t>
+          <t>50417</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26736</t>
+          <t>27457</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51599</t>
+          <t>51864</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59305</t>
+          <t>60553</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94082</t>
+          <t>95514</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60850</t>
+          <t>60697</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95663</t>
+          <t>95419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61119</t>
+          <t>59916</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>95170</t>
+          <t>92969</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>127826</t>
+          <t>128504</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>177403</t>
+          <t>174084</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>170341</t>
+          <t>171621</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>217250</t>
+          <t>217646</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>193442</t>
+          <t>192628</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>236644</t>
+          <t>234541</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>375076</t>
+          <t>374710</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437446</t>
+          <t>440430</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,85%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>150588</t>
+          <t>150254</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>193271</t>
+          <t>197963</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>93887</t>
+          <t>95899</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>131338</t>
+          <t>132422</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>256167</t>
+          <t>250961</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>316666</t>
+          <t>313772</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56492</t>
+          <t>58514</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>89412</t>
+          <t>89996</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27650</t>
+          <t>27155</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51207</t>
+          <t>52189</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89714</t>
+          <t>90773</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>129495</t>
+          <t>132694</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>146854</t>
+          <t>146369</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201403</t>
+          <t>199656</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>244787</t>
+          <t>244498</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>311349</t>
+          <t>313236</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>411102</t>
+          <t>407309</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>490867</t>
+          <t>491481</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>348305</t>
+          <t>344932</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>421152</t>
+          <t>418158</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>534591</t>
+          <t>534068</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>618567</t>
+          <t>622481</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>898898</t>
+          <t>896196</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1015347</t>
+          <t>1011603</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>974825</t>
+          <t>969691</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1079092</t>
+          <t>1075584</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1329416</t>
+          <t>1330085</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1445801</t>
+          <t>1446034</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2338408</t>
+          <t>2339288</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2493953</t>
+          <t>2495632</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>946254</t>
+          <t>947612</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1051415</t>
+          <t>1058307</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>760839</t>
+          <t>762498</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>857056</t>
+          <t>857712</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1731085</t>
+          <t>1733667</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1879996</t>
+          <t>1879199</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>644680</t>
+          <t>645820</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>735910</t>
+          <t>740116</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>290864</t>
+          <t>292854</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>358949</t>
+          <t>359881</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>959103</t>
+          <t>956040</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1067055</t>
+          <t>1071516</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78235</t>
+          <t>79382</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115786</t>
+          <t>116643</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>176990</t>
+          <t>179199</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>232538</t>
+          <t>231277</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>268164</t>
+          <t>266085</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>335866</t>
+          <t>332384</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>239115</t>
+          <t>239350</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>300017</t>
+          <t>296609</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>386480</t>
+          <t>387574</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>454981</t>
+          <t>457623</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>643894</t>
+          <t>640988</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>733183</t>
+          <t>733775</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>259415</t>
+          <t>258647</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>317164</t>
+          <t>319443</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>364305</t>
+          <t>361394</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>432205</t>
+          <t>429421</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>636528</t>
+          <t>636386</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>726603</t>
+          <t>724970</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>189842</t>
+          <t>190259</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>242002</t>
+          <t>242916</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>178851</t>
+          <t>179312</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>231398</t>
+          <t>235911</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>384612</t>
+          <t>383283</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>458957</t>
+          <t>460225</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78576</t>
+          <t>78715</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>115589</t>
+          <t>115341</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81252</t>
+          <t>81635</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>120900</t>
+          <t>122160</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>171462</t>
+          <t>172471</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>225035</t>
+          <t>222752</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>96131</t>
+          <t>94468</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>140077</t>
+          <t>141239</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128550</t>
+          <t>128427</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>178193</t>
+          <t>177594</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>237752</t>
+          <t>233654</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>306208</t>
+          <t>301821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>287915</t>
+          <t>288492</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>356123</t>
+          <t>356926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>385304</t>
+          <t>382361</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>458440</t>
+          <t>455033</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>694571</t>
+          <t>692391</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>796543</t>
+          <t>798339</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>551914</t>
+          <t>551314</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>638772</t>
+          <t>639318</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>533495</t>
+          <t>531063</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>611815</t>
+          <t>610700</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1109363</t>
+          <t>1109582</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1224501</t>
+          <t>1226610</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,07%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>535255</t>
+          <t>535076</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>619090</t>
+          <t>615331</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>371521</t>
+          <t>374898</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>444094</t>
+          <t>447096</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>927681</t>
+          <t>928167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1035466</t>
+          <t>1040295</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>313311</t>
+          <t>316937</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>388018</t>
+          <t>385464</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>171613</t>
+          <t>171731</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>226000</t>
+          <t>228336</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>505365</t>
+          <t>504491</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>594739</t>
+          <t>592057</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>19020</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39906</t>
+          <t>39834</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29363</t>
+          <t>29612</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56583</t>
+          <t>57179</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53844</t>
+          <t>53251</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90096</t>
+          <t>87742</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85485</t>
+          <t>85321</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126184</t>
+          <t>125721</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98122</t>
+          <t>99850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139660</t>
+          <t>138234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>196248</t>
+          <t>195651</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>251883</t>
+          <t>250187</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>129029</t>
+          <t>130661</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>175384</t>
+          <t>174081</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>144873</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>187215</t>
+          <t>187780</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>286390</t>
+          <t>287118</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>347551</t>
+          <t>347825</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120392</t>
+          <t>120832</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>163455</t>
+          <t>162112</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71262</t>
+          <t>70429</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>107064</t>
+          <t>107721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>203769</t>
+          <t>203632</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>259263</t>
+          <t>258562</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39061</t>
+          <t>40528</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68524</t>
+          <t>68705</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30586</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57061</t>
+          <t>56735</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77870</t>
+          <t>76346</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>116735</t>
+          <t>116621</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>211473</t>
+          <t>208998</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>275906</t>
+          <t>271052</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>360218</t>
+          <t>358014</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>442438</t>
+          <t>438662</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>580533</t>
+          <t>588483</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>684315</t>
+          <t>694529</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>646609</t>
+          <t>649480</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>746761</t>
+          <t>751854</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>905871</t>
+          <t>908080</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1015846</t>
+          <t>1018232</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1584517</t>
+          <t>1587802</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1727181</t>
+          <t>1723229</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>975194</t>
+          <t>971559</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1093237</t>
+          <t>1088589</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1075447</t>
+          <t>1077027</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1191793</t>
+          <t>1190447</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2087497</t>
+          <t>2089010</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2242476</t>
+          <t>2246846</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>876996</t>
+          <t>878800</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>985685</t>
+          <t>986403</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>652446</t>
+          <t>653574</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>754642</t>
+          <t>749195</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1562117</t>
+          <t>1561707</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1705565</t>
+          <t>1709813</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>457129</t>
+          <t>453867</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>540796</t>
+          <t>542851</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>303402</t>
+          <t>303739</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>377299</t>
+          <t>376089</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>780195</t>
+          <t>781348</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>889479</t>
+          <t>889820</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60797</t>
+          <t>60254</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91366</t>
+          <t>92675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110107</t>
+          <t>109042</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152725</t>
+          <t>154300</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>180033</t>
+          <t>179187</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>232198</t>
+          <t>232464</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>127274</t>
+          <t>125602</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>171055</t>
+          <t>169209</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234432</t>
+          <t>232652</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>292124</t>
+          <t>292790</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>376332</t>
+          <t>379083</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>446353</t>
+          <t>450673</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>248223</t>
+          <t>253688</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>300566</t>
+          <t>303697</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>325867</t>
+          <t>325665</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>387071</t>
+          <t>388775</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>589181</t>
+          <t>589121</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>674171</t>
+          <t>672964</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,58%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>153725</t>
+          <t>154910</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>200575</t>
+          <t>198343</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166798</t>
+          <t>170318</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>221007</t>
+          <t>222231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>337997</t>
+          <t>336674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>405020</t>
+          <t>407653</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61951</t>
+          <t>62697</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96454</t>
+          <t>95323</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37034</t>
+          <t>36285</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65086</t>
+          <t>64493</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>106879</t>
+          <t>107283</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153300</t>
+          <t>151343</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80053</t>
+          <t>79766</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119161</t>
+          <t>121518</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127747</t>
+          <t>125236</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172702</t>
+          <t>173502</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>216838</t>
+          <t>216590</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>282441</t>
+          <t>280259</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>274777</t>
+          <t>279230</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>343317</t>
+          <t>342201</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>370393</t>
+          <t>372117</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>444692</t>
+          <t>440502</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>670469</t>
+          <t>668772</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>765528</t>
+          <t>764673</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>748205</t>
+          <t>750383</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>836197</t>
+          <t>839035</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>722452</t>
+          <t>719556</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>806369</t>
+          <t>805057</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1495298</t>
+          <t>1499952</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1624565</t>
+          <t>1623158</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,06%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>565592</t>
+          <t>564016</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>648939</t>
+          <t>650229</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>455730</t>
+          <t>455815</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>533184</t>
+          <t>534610</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1051676</t>
+          <t>1053731</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1168211</t>
+          <t>1167303</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>229740</t>
+          <t>230448</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>292811</t>
+          <t>291665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140208</t>
+          <t>141900</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>190494</t>
+          <t>188793</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>383893</t>
+          <t>388240</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>465044</t>
+          <t>466449</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30988</t>
+          <t>29832</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57991</t>
+          <t>57893</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32035</t>
+          <t>31183</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60106</t>
+          <t>58937</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69272</t>
+          <t>69632</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106814</t>
+          <t>106162</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74854</t>
+          <t>75024</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111750</t>
+          <t>111878</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99030</t>
+          <t>98042</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136776</t>
+          <t>138375</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>188286</t>
+          <t>187985</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>242694</t>
+          <t>242683</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>204723</t>
+          <t>203877</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>253114</t>
+          <t>253989</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>188155</t>
+          <t>189111</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>234619</t>
+          <t>236029</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>407898</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>472351</t>
+          <t>476423</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116157</t>
+          <t>119231</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>159286</t>
+          <t>161234</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>107183</t>
+          <t>106002</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>147531</t>
+          <t>147206</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>237178</t>
+          <t>234090</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>292209</t>
+          <t>292872</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29366</t>
+          <t>29342</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57354</t>
+          <t>55992</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36725</t>
+          <t>35732</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62360</t>
+          <t>64601</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71615</t>
+          <t>72717</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110196</t>
+          <t>109819</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>188947</t>
+          <t>189664</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>249112</t>
+          <t>246239</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>288054</t>
+          <t>285220</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>359031</t>
+          <t>357262</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>493857</t>
+          <t>494949</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>587582</t>
+          <t>592927</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>510405</t>
+          <t>507449</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>594248</t>
+          <t>592750</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>734063</t>
+          <t>735668</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>843506</t>
+          <t>840857</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1272733</t>
+          <t>1275623</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1408607</t>
+          <t>1406273</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1242251</t>
+          <t>1240926</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1358477</t>
+          <t>1359878</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1271560</t>
+          <t>1274465</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1387809</t>
+          <t>1393732</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2545760</t>
+          <t>2550128</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2713081</t>
+          <t>2713748</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>869509</t>
+          <t>869103</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>973870</t>
+          <t>976267</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>767730</t>
+          <t>769791</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>869862</t>
+          <t>876349</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1657310</t>
+          <t>1660915</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1810773</t>
+          <t>1810694</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>343343</t>
+          <t>341933</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>415281</t>
+          <t>416482</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>232673</t>
+          <t>231818</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>290679</t>
+          <t>296080</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>594060</t>
+          <t>590038</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>690296</t>
+          <t>686335</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
